--- a/resources/analysis/words/Interesting Words.xlsx
+++ b/resources/analysis/words/Interesting Words.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\mzatt\Projects\Git - v4j-wip\resources\analysis\Rules\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\mzatt\Projects\Git - v4j\resources\analysis\words\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4567F2AB-6561-4774-8280-135B0D5FF227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A86192D6-9663-4323-B464-599E4748C812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="897" xr2:uid="{BDECC11F-9658-4540-8D2A-5E200A7D7849}"/>
   </bookViews>
@@ -83,168 +83,6 @@
     <t>Random text - control</t>
   </si>
   <si>
-    <t>%Interesting(fromBegin(0))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(1))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(2))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(3))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(4))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(5))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(6))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(7))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(8))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(9))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(10))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(11))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(12))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(13))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(14))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(15))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(16))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(17))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(18))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(19))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(20))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(21))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(22))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(23))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(24))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(25))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromBegin(26))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(0))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(1))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(2))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(3))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(4))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(5))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(6))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(7))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(8))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(9))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(10))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(11))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(12))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(13))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(14))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(15))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(16))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(17))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(18))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(19))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(20))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(21))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(22))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(23))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(24))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(25))</t>
-  </si>
-  <si>
-    <t>%Interesting(fromEnd(26))</t>
-  </si>
-  <si>
     <t>Normal text from the beginning (all lines)</t>
   </si>
   <si>
@@ -269,107 +107,272 @@
     <t>% of interesting words by position in paragraph.</t>
   </si>
   <si>
-    <t>%Interesting(line 0)</t>
+    <t>line 0)</t>
   </si>
   <si>
-    <t>%Interesting(line 1)</t>
+    <t>line 1)</t>
   </si>
   <si>
-    <t>%Interesting(line 2)</t>
+    <t>line 2)</t>
   </si>
   <si>
-    <t>%Interesting(line 3)</t>
+    <t>line 3)</t>
   </si>
   <si>
-    <t>%Interesting(line 4)</t>
+    <t>line 4)</t>
   </si>
   <si>
-    <t>%Interesting(line 5)</t>
+    <t>line 5)</t>
   </si>
   <si>
-    <t>%Interesting(line 6)</t>
+    <t>line 6)</t>
   </si>
   <si>
-    <t>%Interesting(line 7)</t>
+    <t>line 7)</t>
   </si>
   <si>
-    <t>%Interesting(line 8)</t>
+    <t>line 8)</t>
   </si>
   <si>
-    <t>%Interesting(line 9)</t>
+    <t>line 9)</t>
   </si>
   <si>
-    <t>%Interesting(line 10)</t>
+    <t>line 10)</t>
   </si>
   <si>
-    <t>%Interesting(line 11)</t>
+    <t>line 11)</t>
   </si>
   <si>
-    <t>%Interesting(line 12)</t>
+    <t>line 12)</t>
   </si>
   <si>
-    <t>%Interesting(line 13)</t>
+    <t>line 13)</t>
   </si>
   <si>
-    <t>%Interesting(line 14)</t>
+    <t>line 14)</t>
   </si>
   <si>
-    <t>%Interesting(line 15)</t>
+    <t>line 15)</t>
   </si>
   <si>
-    <t>%Interesting(line 16)</t>
+    <t>line 16)</t>
   </si>
   <si>
-    <t>%Interesting(line 17)</t>
+    <t>line 17)</t>
   </si>
   <si>
-    <t>%Interesting(line 18)</t>
+    <t>line 18)</t>
   </si>
   <si>
-    <t>%Interesting(line 19)</t>
+    <t>line 19)</t>
   </si>
   <si>
-    <t>%Interesting(line 20)</t>
+    <t>line 20)</t>
   </si>
   <si>
-    <t>%Interesting(line 21)</t>
+    <t>line 21)</t>
   </si>
   <si>
-    <t>%Interesting(line 22)</t>
+    <t>line 22)</t>
   </si>
   <si>
-    <t>%Interesting(line 23)</t>
+    <t>line 23)</t>
   </si>
   <si>
-    <t>%Interesting(line 24)</t>
+    <t>line 24)</t>
   </si>
   <si>
-    <t>%Interesting(line 25)</t>
+    <t>line 25)</t>
   </si>
   <si>
-    <t>%Interesting(line 26)</t>
+    <t>line 26)</t>
   </si>
   <si>
-    <t>%Interesting(line 27)</t>
+    <t>line 27)</t>
   </si>
   <si>
-    <t>%Interesting(line 28)</t>
+    <t>line 28)</t>
   </si>
   <si>
-    <t>%Interesting(line 29)</t>
+    <t>line 29)</t>
   </si>
   <si>
-    <t>%Interesting(line 30)</t>
+    <t>line 30)</t>
   </si>
   <si>
-    <t>%Interesting(line 31)</t>
+    <t>line 31)</t>
+  </si>
+  <si>
+    <t>fromBegin(0)</t>
+  </si>
+  <si>
+    <t>fromBegin(1)</t>
+  </si>
+  <si>
+    <t>fromBegin(2)</t>
+  </si>
+  <si>
+    <t>fromBegin(3)</t>
+  </si>
+  <si>
+    <t>fromBegin(4)</t>
+  </si>
+  <si>
+    <t>fromBegin(5)</t>
+  </si>
+  <si>
+    <t>fromBegin(6)</t>
+  </si>
+  <si>
+    <t>fromBegin(7)</t>
+  </si>
+  <si>
+    <t>fromBegin(8)</t>
+  </si>
+  <si>
+    <t>fromBegin(9)</t>
+  </si>
+  <si>
+    <t>fromBegin(10)</t>
+  </si>
+  <si>
+    <t>fromBegin(11)</t>
+  </si>
+  <si>
+    <t>fromBegin(12)</t>
+  </si>
+  <si>
+    <t>fromBegin(13)</t>
+  </si>
+  <si>
+    <t>fromBegin(14)</t>
+  </si>
+  <si>
+    <t>fromBegin(15)</t>
+  </si>
+  <si>
+    <t>fromBegin(16)</t>
+  </si>
+  <si>
+    <t>fromBegin(17)</t>
+  </si>
+  <si>
+    <t>fromBegin(18)</t>
+  </si>
+  <si>
+    <t>fromBegin(19)</t>
+  </si>
+  <si>
+    <t>fromBegin(20)</t>
+  </si>
+  <si>
+    <t>fromBegin(21)</t>
+  </si>
+  <si>
+    <t>fromBegin(22)</t>
+  </si>
+  <si>
+    <t>fromBegin(23)</t>
+  </si>
+  <si>
+    <t>fromBegin(24)</t>
+  </si>
+  <si>
+    <t>fromBegin(25)</t>
+  </si>
+  <si>
+    <t>fromBegin(26)</t>
+  </si>
+  <si>
+    <t>fromEnd(0)</t>
+  </si>
+  <si>
+    <t>fromEnd(1)</t>
+  </si>
+  <si>
+    <t>fromEnd(2)</t>
+  </si>
+  <si>
+    <t>fromEnd(3)</t>
+  </si>
+  <si>
+    <t>fromEnd(4)</t>
+  </si>
+  <si>
+    <t>fromEnd(5)</t>
+  </si>
+  <si>
+    <t>fromEnd(6)</t>
+  </si>
+  <si>
+    <t>fromEnd(7)</t>
+  </si>
+  <si>
+    <t>fromEnd(8)</t>
+  </si>
+  <si>
+    <t>fromEnd(9)</t>
+  </si>
+  <si>
+    <t>fromEnd(10)</t>
+  </si>
+  <si>
+    <t>fromEnd(11)</t>
+  </si>
+  <si>
+    <t>fromEnd(12)</t>
+  </si>
+  <si>
+    <t>fromEnd(13)</t>
+  </si>
+  <si>
+    <t>fromEnd(14)</t>
+  </si>
+  <si>
+    <t>fromEnd(15)</t>
+  </si>
+  <si>
+    <t>fromEnd(16)</t>
+  </si>
+  <si>
+    <t>fromEnd(17)</t>
+  </si>
+  <si>
+    <t>fromEnd(18)</t>
+  </si>
+  <si>
+    <t>fromEnd(19)</t>
+  </si>
+  <si>
+    <t>fromEnd(20)</t>
+  </si>
+  <si>
+    <t>fromEnd(21)</t>
+  </si>
+  <si>
+    <t>fromEnd(22)</t>
+  </si>
+  <si>
+    <t>fromEnd(23)</t>
+  </si>
+  <si>
+    <t>fromEnd(24)</t>
+  </si>
+  <si>
+    <t>fromEnd(25)</t>
+  </si>
+  <si>
+    <t>fromEnd(26)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +393,13 @@
       <color rgb="FF000000"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -415,21 +425,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -556,37 +569,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -595,7 +608,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$12:$L$12</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.53343465045592697</c:v>
@@ -672,37 +685,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -711,7 +724,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$13:$L$13</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.46250000000000002</c:v>
@@ -788,37 +801,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -827,7 +840,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$14:$L$14</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.53675730110775399</c:v>
@@ -904,37 +917,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -943,7 +956,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$15:$L$15</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.69343065693430594</c:v>
@@ -1020,37 +1033,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1059,7 +1072,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$16:$L$16</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.67362924281984304</c:v>
@@ -1190,7 +1203,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1420,31 +1433,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1453,7 +1466,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$79:$J$79</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.16427640156453699</c:v>
@@ -1524,31 +1537,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1557,7 +1570,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$80:$J$80</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.34557235421166299</c:v>
@@ -1628,31 +1641,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1661,7 +1674,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$81:$J$81</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.303006329113924</c:v>
@@ -1732,31 +1745,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1765,7 +1778,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$82:$J$82</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.29432013769363102</c:v>
@@ -1836,31 +1849,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1869,7 +1882,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$83:$J$83</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.235970250169033</c:v>
@@ -1994,7 +2007,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2224,37 +2237,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2263,7 +2276,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$50:$L$50</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.15754189944134001</c:v>
@@ -2340,37 +2353,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2379,7 +2392,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$51:$L$51</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.35799522673030998</c:v>
@@ -2456,37 +2469,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2495,7 +2508,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$52:$L$52</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.21608040201004999</c:v>
@@ -2572,37 +2585,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2611,7 +2624,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$53:$L$53</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.28612716763005702</c:v>
@@ -2688,37 +2701,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2727,7 +2740,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$54:$L$54</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.23804971319311599</c:v>
@@ -2858,7 +2871,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3083,37 +3096,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3122,7 +3135,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$59:$L$59</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.18973214285714199</c:v>
@@ -3199,37 +3212,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3238,7 +3251,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$60:$L$60</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.34198113207547098</c:v>
@@ -3315,37 +3328,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3354,7 +3367,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$61:$L$61</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.244949494949494</c:v>
@@ -3431,37 +3444,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3470,7 +3483,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$62:$L$62</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.27034883720930197</c:v>
@@ -3547,37 +3560,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3586,7 +3599,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$63:$L$63</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.242013552758954</c:v>
@@ -3717,7 +3730,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3947,37 +3960,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3986,7 +3999,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$21:$L$21</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.49773071104387201</c:v>
@@ -4063,37 +4076,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4102,7 +4115,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$22:$L$22</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.55844155844155796</c:v>
@@ -4179,37 +4192,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4218,7 +4231,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$23:$L$23</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.56905503634475596</c:v>
@@ -4295,37 +4308,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4334,7 +4347,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$24:$L$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.50364963503649596</c:v>
@@ -4411,37 +4424,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4450,7 +4463,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$25:$L$25</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.54400000000000004</c:v>
@@ -4581,7 +4594,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4811,37 +4824,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4850,7 +4863,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$32:$L$32</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.535433070866141</c:v>
@@ -4927,37 +4940,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4966,7 +4979,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$33:$L$33</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.64285714285714202</c:v>
@@ -5043,37 +5056,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5082,7 +5095,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$34:$L$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.560165975103734</c:v>
@@ -5159,37 +5172,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5198,7 +5211,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$35:$L$35</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.70845481049562598</c:v>
@@ -5275,37 +5288,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5314,7 +5327,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$36:$L$36</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.73346116970277997</c:v>
@@ -5445,7 +5458,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5675,37 +5688,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5714,7 +5727,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$41:$L$41</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.48876404494381998</c:v>
@@ -5791,37 +5804,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5830,7 +5843,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$42:$L$42</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.683544303797468</c:v>
@@ -5907,37 +5920,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5946,7 +5959,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$43:$L$43</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.574595055413469</c:v>
@@ -6023,37 +6036,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6062,7 +6075,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$44:$L$44</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.53372434017595305</c:v>
@@ -6139,37 +6152,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6178,7 +6191,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$45:$L$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.556640625</c:v>
@@ -6309,7 +6322,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6539,37 +6552,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6578,7 +6591,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$50:$L$50</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.15754189944134001</c:v>
@@ -6655,37 +6668,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6694,7 +6707,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$51:$L$51</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.35799522673030998</c:v>
@@ -6771,37 +6784,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6810,7 +6823,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$52:$L$52</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.21608040201004999</c:v>
@@ -6887,37 +6900,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6926,7 +6939,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$53:$L$53</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.28612716763005702</c:v>
@@ -7003,37 +7016,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromBegin(0))</c:v>
+                  <c:v>fromBegin(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromBegin(1))</c:v>
+                  <c:v>fromBegin(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromBegin(2))</c:v>
+                  <c:v>fromBegin(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromBegin(3))</c:v>
+                  <c:v>fromBegin(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromBegin(4))</c:v>
+                  <c:v>fromBegin(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromBegin(5))</c:v>
+                  <c:v>fromBegin(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromBegin(6))</c:v>
+                  <c:v>fromBegin(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromBegin(7))</c:v>
+                  <c:v>fromBegin(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromBegin(8))</c:v>
+                  <c:v>fromBegin(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromBegin(9))</c:v>
+                  <c:v>fromBegin(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromBegin(10))</c:v>
+                  <c:v>fromBegin(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7042,7 +7055,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$54:$L$54</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.23804971319311599</c:v>
@@ -7173,7 +7186,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -7398,37 +7411,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7437,7 +7450,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$59:$L$59</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.18973214285714199</c:v>
@@ -7514,37 +7527,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7553,7 +7566,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$60:$L$60</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.34198113207547098</c:v>
@@ -7630,37 +7643,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7669,7 +7682,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$61:$L$61</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.244949494949494</c:v>
@@ -7746,37 +7759,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7785,7 +7798,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$62:$L$62</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.27034883720930197</c:v>
@@ -7862,37 +7875,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(fromEnd(0))</c:v>
+                  <c:v>fromEnd(0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(fromEnd(1))</c:v>
+                  <c:v>fromEnd(1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(fromEnd(2))</c:v>
+                  <c:v>fromEnd(2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(fromEnd(3))</c:v>
+                  <c:v>fromEnd(3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(fromEnd(4))</c:v>
+                  <c:v>fromEnd(4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(fromEnd(5))</c:v>
+                  <c:v>fromEnd(5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(fromEnd(6))</c:v>
+                  <c:v>fromEnd(6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(fromEnd(7))</c:v>
+                  <c:v>fromEnd(7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(fromEnd(8))</c:v>
+                  <c:v>fromEnd(8)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>%Interesting(fromEnd(9))</c:v>
+                  <c:v>fromEnd(9)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>%Interesting(fromEnd(10))</c:v>
+                  <c:v>fromEnd(10)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7901,7 +7914,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$63:$L$63</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.242013552758954</c:v>
@@ -8032,7 +8045,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -8264,31 +8277,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8297,7 +8310,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$70:$J$70</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.35356200527704401</c:v>
@@ -8368,31 +8381,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8401,7 +8414,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$71:$J$71</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.51521739130434696</c:v>
@@ -8472,31 +8485,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8505,7 +8518,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$72:$J$72</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.46482213438735098</c:v>
@@ -8576,31 +8589,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8609,7 +8622,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$73:$J$73</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.52869565217391301</c:v>
@@ -8680,31 +8693,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>%Interesting(line 0)</c:v>
+                  <c:v>line 0)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>%Interesting(line 1)</c:v>
+                  <c:v>line 1)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>%Interesting(line 2)</c:v>
+                  <c:v>line 2)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>%Interesting(line 3)</c:v>
+                  <c:v>line 3)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>%Interesting(line 4)</c:v>
+                  <c:v>line 4)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>%Interesting(line 5)</c:v>
+                  <c:v>line 5)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>%Interesting(line 6)</c:v>
+                  <c:v>line 6)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>%Interesting(line 7)</c:v>
+                  <c:v>line 7)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>%Interesting(line 8)</c:v>
+                  <c:v>line 8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8713,7 +8726,7 @@
             <c:numRef>
               <c:f>InterestingWords!$B$74:$J$74</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.441046551138294</c:v>
@@ -8838,7 +8851,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -14835,15 +14848,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>171450</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
+      <xdr:colOff>381000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
+      <xdr:rowOff>180974</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14873,15 +14886,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>171450</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
+      <xdr:colOff>381000</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15213,20 +15226,23 @@
   </sheetPr>
   <dimension ref="A1:AG85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="3"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -15240,15 +15256,15 @@
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
+      <c r="A6" s="4"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -15256,141 +15272,141 @@
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
+      <c r="A10" s="4"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>29</v>
-      </c>
-      <c r="R11" t="s">
-        <v>30</v>
-      </c>
-      <c r="S11" t="s">
-        <v>31</v>
-      </c>
-      <c r="T11" t="s">
-        <v>32</v>
-      </c>
-      <c r="U11" t="s">
-        <v>33</v>
-      </c>
-      <c r="V11" t="s">
-        <v>34</v>
-      </c>
-      <c r="W11" t="s">
-        <v>35</v>
-      </c>
-      <c r="X11" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>40</v>
+      <c r="B11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>0.53343465045592697</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>0.335832083958021</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>0.177978883861236</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <v>0.170212765957446</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="3">
         <v>0.183514774494556</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3">
         <v>0.14925373134328301</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="3">
         <v>0.14338235294117599</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="3">
         <v>0.13646055437100199</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="3">
         <v>0.20209973753280799</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="3">
         <v>0.233333333333333</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="3">
         <v>0.221518987341772</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="3">
         <v>0.20512820512820501</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="3">
         <v>0.27777777777777701</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="3">
         <v>0.58333333333333304</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -15398,85 +15414,85 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>0.46250000000000002</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>0.36842105263157798</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
         <v>0.31360946745562102</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="3">
         <v>0.26627218934911201</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="3">
         <v>0.30625000000000002</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="3">
         <v>0.34838709677419299</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="3">
         <v>0.30496453900709197</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="3">
         <v>0.31159420289855</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="3">
         <v>0.32758620689655099</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="3">
         <v>0.36363636363636298</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="3">
         <v>0.29545454545454503</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="3">
         <v>0.29032258064516098</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="3">
         <v>0.2</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="3">
         <v>0.26086956521739102</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="3">
         <v>0.13043478260869501</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="3">
         <v>0.3125</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="3">
         <v>0.46153846153846101</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="3">
         <v>9.0909090909090898E-2</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="3">
         <v>0.5</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="3">
         <v>0.625</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="3">
         <v>0.5</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="3">
         <v>0</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="3">
         <v>0.5</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="3">
         <v>0.25</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="3">
         <v>0.25</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="3">
         <v>0.5</v>
       </c>
-      <c r="AB13">
+      <c r="AB13" s="3">
         <v>0</v>
       </c>
     </row>
@@ -15484,40 +15500,40 @@
       <c r="A14" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>0.53675730110775399</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <v>0.36060606060605999</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="3">
         <v>0.32815734989647999</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="3">
         <v>0.191873589164785</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="3">
         <v>0.24833110814419199</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="3">
         <v>0.25166666666666598</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="3">
         <v>0.22850678733031601</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="3">
         <v>0.27450980392156799</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="3">
         <v>0.24456521739130399</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="3">
         <v>0.19230769230769201</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="3">
         <v>0.36</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -15525,46 +15541,46 @@
       <c r="A15" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>0.69343065693430594</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <v>0.34545454545454501</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="3">
         <v>0.24820143884891999</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="3">
         <v>0.308550185873605</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="3">
         <v>0.30434782608695599</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="3">
         <v>0.24137931034482701</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="3">
         <v>0.26521739130434702</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="3">
         <v>0.25</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="3">
         <v>0.27225130890052301</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="3">
         <v>0.28025477707006302</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="3">
         <v>0.232558139534883</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="3">
         <v>0.29787234042553101</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="3">
         <v>0.5</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="3">
         <v>0.42857142857142799</v>
       </c>
     </row>
@@ -15572,57 +15588,57 @@
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>0.67362924281984304</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <v>0.388311688311688</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="3">
         <v>0.26233766233766198</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="3">
         <v>0.216644649933949</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="3">
         <v>0.27372764786795001</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="3">
         <v>0.23580786026200801</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="3">
         <v>0.19815668202764899</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="3">
         <v>0.181364392678868</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="3">
         <v>0.194192377495462</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="3">
         <v>0.27600849256900201</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="3">
         <v>0.29281767955801102</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="3">
         <v>0.33009708737864002</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="3">
         <v>0.42666666666666597</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="3">
         <v>0.56521739130434701</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="3">
         <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
+      <c r="A17" s="4"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
@@ -15630,141 +15646,141 @@
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
+      <c r="A19" s="4"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H20" t="s">
-        <v>47</v>
-      </c>
-      <c r="I20" t="s">
-        <v>48</v>
-      </c>
-      <c r="J20" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" t="s">
-        <v>51</v>
-      </c>
-      <c r="M20" t="s">
-        <v>52</v>
-      </c>
-      <c r="N20" t="s">
-        <v>53</v>
-      </c>
-      <c r="O20" t="s">
-        <v>54</v>
-      </c>
-      <c r="P20" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>56</v>
-      </c>
-      <c r="R20" t="s">
-        <v>57</v>
-      </c>
-      <c r="S20" t="s">
-        <v>58</v>
-      </c>
-      <c r="T20" t="s">
-        <v>59</v>
-      </c>
-      <c r="U20" t="s">
-        <v>60</v>
-      </c>
-      <c r="V20" t="s">
-        <v>61</v>
-      </c>
-      <c r="W20" t="s">
-        <v>62</v>
-      </c>
-      <c r="X20" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>67</v>
+      <c r="B20" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>0.49773071104387201</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>0.197247706422018</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
         <v>0.12310030395136699</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="3">
         <v>0.11846153846153799</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="3">
         <v>0.140845070422535</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="3">
         <v>0.108552631578947</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="3">
         <v>0.13503649635036399</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="3">
         <v>0.18012422360248401</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="3">
         <v>0.123036649214659</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="3">
         <v>0.19548872180451099</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="3">
         <v>0.26086956521739102</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="3">
         <v>0.3125</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="3">
         <v>0.157894736842105</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="3">
         <v>0.5</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="3">
         <v>0.33333333333333298</v>
       </c>
     </row>
@@ -15772,85 +15788,85 @@
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="3">
         <v>0.55844155844155796</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="3">
         <v>0.27810650887573901</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="3">
         <v>0.30409356725146103</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="3">
         <v>0.34146341463414598</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="3">
         <v>0.23749999999999999</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="3">
         <v>0.259493670886075</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="3">
         <v>0.30612244897959101</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="3">
         <v>0.36496350364963498</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="3">
         <v>0.33913043478260801</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="3">
         <v>0.35135135135135098</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="3">
         <v>0.28571428571428498</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="3">
         <v>0.14705882352941099</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="3">
         <v>0.36</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="3">
         <v>8.3333333333333301E-2</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="3">
         <v>0.36363636363636298</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="3">
         <v>0.23529411764705799</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="3">
         <v>0.25</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="3">
         <v>0.27272727272727199</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="3">
         <v>0.25</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="3">
         <v>0.125</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="3">
         <v>0.57142857142857095</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="3">
         <v>0.71428571428571397</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="3">
         <v>0.25</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="3">
         <v>0.25</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="3">
         <v>0.5</v>
       </c>
-      <c r="AB22">
+      <c r="AB22" s="3">
         <v>0</v>
       </c>
     </row>
@@ -15858,40 +15874,40 @@
       <c r="A23" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="3">
         <v>0.56905503634475596</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="3">
         <v>0.29817444219066902</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="3">
         <v>0.20389344262295001</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="3">
         <v>0.24103139013452901</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="3">
         <v>0.25202156334231801</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="3">
         <v>0.204283360790774</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="3">
         <v>0.27252252252252201</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="3">
         <v>0.25796178343949</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="3">
         <v>0.21390374331550799</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="3">
         <v>0.13750000000000001</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="3">
         <v>0.25</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="3">
         <v>0.16666666666666599</v>
       </c>
     </row>
@@ -15899,46 +15915,46 @@
       <c r="A24" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="3">
         <v>0.50364963503649596</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="3">
         <v>0.298561151079136</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="3">
         <v>0.27472527472527403</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="3">
         <v>0.31501831501831501</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="3">
         <v>0.24899598393574199</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="3">
         <v>0.30801687763712998</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="3">
         <v>0.32</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="3">
         <v>0.30188679245283001</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="3">
         <v>0.30729166666666602</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="3">
         <v>0.34394904458598702</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="3">
         <v>0.390804597701149</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="3">
         <v>0.25</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="3">
         <v>0.38888888888888801</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -15946,207 +15962,207 @@
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="3">
         <v>0.54400000000000004</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="3">
         <v>0.22976501305482999</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="3">
         <v>0.247730220492866</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="3">
         <v>0.176392572944297</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="3">
         <v>0.20272108843537401</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="3">
         <v>0.172166427546628</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="3">
         <v>0.17829457364341</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="3">
         <v>0.19765494137353401</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="3">
         <v>0.181985294117647</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="3">
         <v>0.28099173553718998</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="3">
         <v>0.30081300813008099</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="3">
         <v>0.37864077669902901</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="3">
         <v>0.35897435897435898</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="3">
         <v>0.476190476190476</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="3">
         <v>0.5</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="3">
         <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
+      <c r="A26" s="4"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
+      <c r="A28" s="4"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
+      <c r="A30" s="4"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" t="s">
-        <v>21</v>
-      </c>
-      <c r="J31" t="s">
-        <v>22</v>
-      </c>
-      <c r="K31" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" t="s">
-        <v>24</v>
-      </c>
-      <c r="M31" t="s">
-        <v>25</v>
-      </c>
-      <c r="N31" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P31" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>29</v>
-      </c>
-      <c r="R31" t="s">
-        <v>30</v>
-      </c>
-      <c r="S31" t="s">
-        <v>31</v>
-      </c>
-      <c r="T31" t="s">
-        <v>32</v>
-      </c>
-      <c r="U31" t="s">
-        <v>33</v>
-      </c>
-      <c r="V31" t="s">
-        <v>34</v>
-      </c>
-      <c r="W31" t="s">
-        <v>35</v>
-      </c>
-      <c r="X31" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>40</v>
+      <c r="B31" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="U31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="V31" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="W31" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="X31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z31" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB31" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="3">
         <v>0.535433070866141</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="3">
         <v>0.363870967741935</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="3">
         <v>0.187582562747688</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="3">
         <v>0.21179624664879301</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="3">
         <v>0.14657534246575299</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="3">
         <v>0.14537444933920701</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="3">
         <v>0.15942028985507201</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="3">
         <v>0.12969924812030001</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="3">
         <v>0.25115207373271797</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="3">
         <v>0.19805194805194801</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="3">
         <v>0.27932960893854702</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="3">
         <v>0.232558139534883</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="3">
         <v>0.2</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="3">
         <v>0.5</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -16154,85 +16170,85 @@
       <c r="A33" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="3">
         <v>0.64285714285714202</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="3">
         <v>0.391489361702127</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="3">
         <v>0.323943661971831</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="3">
         <v>0.26760563380281599</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="3">
         <v>0.31527093596059103</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="3">
         <v>0.30769230769230699</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="3">
         <v>0.32432432432432401</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="3">
         <v>0.29050279329608902</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="3">
         <v>0.335616438356164</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="3">
         <v>0.4</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="3">
         <v>0.31481481481481399</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="3">
         <v>0.32432432432432401</v>
       </c>
-      <c r="N33">
+      <c r="N33" s="3">
         <v>0.29411764705882298</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="3">
         <v>0.29032258064516098</v>
       </c>
-      <c r="P33">
+      <c r="P33" s="3">
         <v>9.375E-2</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="3">
         <v>0.27272727272727199</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="3">
         <v>0.44444444444444398</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="3">
         <v>0.29411764705882298</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="3">
         <v>0.28571428571428498</v>
       </c>
-      <c r="U33">
+      <c r="U33" s="3">
         <v>0.64285714285714202</v>
       </c>
-      <c r="V33">
+      <c r="V33" s="3">
         <v>0.41666666666666602</v>
       </c>
-      <c r="W33">
+      <c r="W33" s="3">
         <v>0.14285714285714199</v>
       </c>
-      <c r="X33">
+      <c r="X33" s="3">
         <v>0.375</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="Z33">
+      <c r="Z33" s="3">
         <v>0.2</v>
       </c>
-      <c r="AA33">
+      <c r="AA33" s="3">
         <v>0.5</v>
       </c>
-      <c r="AB33">
+      <c r="AB33" s="3">
         <v>1</v>
       </c>
     </row>
@@ -16240,40 +16256,40 @@
       <c r="A34" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="3">
         <v>0.560165975103734</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="3">
         <v>0.37670068027210801</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="3">
         <v>0.31064572425828901</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="3">
         <v>0.198292220113852</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="3">
         <v>0.249176728869374</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <v>0.24899598393574199</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="3">
         <v>0.26595744680851002</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="3">
         <v>0.32070707070707</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="3">
         <v>0.25</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="3">
         <v>0.25242718446601897</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="3">
         <v>0.36666666666666597</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -16281,46 +16297,46 @@
       <c r="A35" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="3">
         <v>0.70845481049562598</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="3">
         <v>0.36470588235294099</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="3">
         <v>0.27246376811594197</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="3">
         <v>0.319402985074626</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="3">
         <v>0.319620253164556</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <v>0.298969072164948</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="3">
         <v>0.29065743944636602</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="3">
         <v>0.29104477611940299</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="3">
         <v>0.26859504132231399</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="3">
         <v>0.31413612565444998</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="3">
         <v>0.207920792079207</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="3">
         <v>0.30357142857142799</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="3">
         <v>0.52173913043478204</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="3">
         <v>0.375</v>
       </c>
     </row>
@@ -16328,199 +16344,199 @@
       <c r="A36" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="3">
         <v>0.73346116970277997</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="3">
         <v>0.37832699619771798</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="3">
         <v>0.27931363203050502</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="3">
         <v>0.23314065510597301</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="3">
         <v>0.235764235764235</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="3">
         <v>0.24170124481327801</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="3">
         <v>0.203007518796992</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="3">
         <v>0.239452679589509</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="3">
         <v>0.22794117647058801</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="3">
         <v>0.32714285714285701</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="3">
         <v>0.31547619047619002</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="3">
         <v>0.41281138790035499</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="3">
         <v>0.48351648351648302</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="3">
         <v>0.51851851851851805</v>
       </c>
-      <c r="P36">
+      <c r="P36" s="3">
         <v>0.42857142857142799</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
+      <c r="A37" s="4"/>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
+      <c r="A39" s="4"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B40" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" t="s">
-        <v>43</v>
-      </c>
-      <c r="E40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F40" t="s">
-        <v>45</v>
-      </c>
-      <c r="G40" t="s">
-        <v>46</v>
-      </c>
-      <c r="H40" t="s">
-        <v>47</v>
-      </c>
-      <c r="I40" t="s">
-        <v>48</v>
-      </c>
-      <c r="J40" t="s">
-        <v>49</v>
-      </c>
-      <c r="K40" t="s">
-        <v>50</v>
-      </c>
-      <c r="L40" t="s">
-        <v>51</v>
-      </c>
-      <c r="M40" t="s">
-        <v>52</v>
-      </c>
-      <c r="N40" t="s">
-        <v>53</v>
-      </c>
-      <c r="O40" t="s">
-        <v>54</v>
-      </c>
-      <c r="P40" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>56</v>
-      </c>
-      <c r="R40" t="s">
-        <v>57</v>
-      </c>
-      <c r="S40" t="s">
-        <v>58</v>
-      </c>
-      <c r="T40" t="s">
-        <v>59</v>
-      </c>
-      <c r="U40" t="s">
-        <v>60</v>
-      </c>
-      <c r="V40" t="s">
-        <v>61</v>
-      </c>
-      <c r="W40" t="s">
-        <v>62</v>
-      </c>
-      <c r="X40" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>67</v>
+      <c r="B40" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="U40" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V40" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="W40" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="X40" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y40" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z40" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA40" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB40" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="3">
         <v>0.48876404494381998</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="3">
         <v>0.208115183246073</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="3">
         <v>0.12080536912751599</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="3">
         <v>0.13802435723951201</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="3">
         <v>0.13617606602475901</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="3">
         <v>0.15552325581395299</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="3">
         <v>0.12959999999999999</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="3">
         <v>0.25683060109289602</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="3">
         <v>0.144495412844036</v>
       </c>
-      <c r="K41">
+      <c r="K41" s="3">
         <v>0.21052631578947301</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="3">
         <v>0.29834254143646399</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="3">
         <v>0.34090909090909</v>
       </c>
-      <c r="N41">
+      <c r="N41" s="3">
         <v>0.26190476190476097</v>
       </c>
-      <c r="O41">
+      <c r="O41" s="3">
         <v>0.5</v>
       </c>
-      <c r="P41">
+      <c r="P41" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -16528,85 +16544,85 @@
       <c r="A42" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="3">
         <v>0.683544303797468</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="3">
         <v>0.30212765957446802</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="3">
         <v>0.30909090909090903</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="3">
         <v>0.31219512195121901</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="3">
         <v>0.30392156862745001</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <v>0.28140703517587901</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="3">
         <v>0.32105263157894698</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="3">
         <v>0.40571428571428497</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="3">
         <v>0.37931034482758602</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="3">
         <v>0.375</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="3">
         <v>0.31666666666666599</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="3">
         <v>0.209302325581395</v>
       </c>
-      <c r="N42">
+      <c r="N42" s="3">
         <v>0.41176470588235198</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="3">
         <v>0.16129032258064499</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="3">
         <v>0.31034482758620602</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="3">
         <v>0.4</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="S42">
+      <c r="S42" s="3">
         <v>0.29411764705882298</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="3">
         <v>0.30769230769230699</v>
       </c>
-      <c r="U42">
+      <c r="U42" s="3">
         <v>0.16666666666666599</v>
       </c>
-      <c r="V42">
+      <c r="V42" s="3">
         <v>0.5</v>
       </c>
-      <c r="W42">
+      <c r="W42" s="3">
         <v>0.5</v>
       </c>
-      <c r="X42">
+      <c r="X42" s="3">
         <v>0.14285714285714199</v>
       </c>
-      <c r="Y42">
+      <c r="Y42" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="Z42">
+      <c r="Z42" s="3">
         <v>0.4</v>
       </c>
-      <c r="AA42">
+      <c r="AA42" s="3">
         <v>0.5</v>
       </c>
-      <c r="AB42">
+      <c r="AB42" s="3">
         <v>0</v>
       </c>
     </row>
@@ -16614,40 +16630,40 @@
       <c r="A43" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="3">
         <v>0.574595055413469</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="3">
         <v>0.29166666666666602</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="3">
         <v>0.22164502164502101</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="3">
         <v>0.208450704225352</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="3">
         <v>0.22666666666666599</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="3">
         <v>0.22709163346613501</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="3">
         <v>0.29100529100529099</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="3">
         <v>0.28571428571428498</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="3">
         <v>0.257261410788381</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="3">
         <v>0.26213592233009703</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="3">
         <v>0.33333333333333298</v>
       </c>
     </row>
@@ -16655,46 +16671,46 @@
       <c r="A44" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="3">
         <v>0.53372434017595305</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="3">
         <v>0.31395348837209303</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="3">
         <v>0.28823529411764698</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="3">
         <v>0.31268436578170999</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="3">
         <v>0.269230769230769</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <v>0.30434782608695599</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="3">
         <v>0.34965034965034902</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="3">
         <v>0.328358208955223</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="3">
         <v>0.31799163179916301</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="3">
         <v>0.34554973821989499</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="3">
         <v>0.38</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="3">
         <v>0.305084745762711</v>
       </c>
-      <c r="N44">
+      <c r="N44" s="3">
         <v>0.56521739130434701</v>
       </c>
-      <c r="O44">
+      <c r="O44" s="3">
         <v>0.57142857142857095</v>
       </c>
     </row>
@@ -16702,57 +16718,57 @@
       <c r="A45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="3">
         <v>0.556640625</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="3">
         <v>0.25650916104146498</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="3">
         <v>0.23193916349809801</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="3">
         <v>0.18243243243243201</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="3">
         <v>0.21541501976284499</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <v>0.2119341563786</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="3">
         <v>0.20652173913043401</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="3">
         <v>0.18339100346020701</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="3">
         <v>0.20245398773006101</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="3">
         <v>0.27184466019417403</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="3">
         <v>0.34429400386847198</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="3">
         <v>0.41071428571428498</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="3">
         <v>0.45833333333333298</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="3">
         <v>0.52</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="3">
         <v>0.57142857142857095</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
+      <c r="A46" s="4"/>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
@@ -16760,141 +16776,141 @@
       </c>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
+      <c r="A48" s="4"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" t="s">
-        <v>16</v>
-      </c>
-      <c r="E49" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" t="s">
-        <v>21</v>
-      </c>
-      <c r="J49" t="s">
-        <v>22</v>
-      </c>
-      <c r="K49" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49" t="s">
-        <v>24</v>
-      </c>
-      <c r="M49" t="s">
-        <v>25</v>
-      </c>
-      <c r="N49" t="s">
-        <v>26</v>
-      </c>
-      <c r="O49" t="s">
-        <v>27</v>
-      </c>
-      <c r="P49" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>29</v>
-      </c>
-      <c r="R49" t="s">
-        <v>30</v>
-      </c>
-      <c r="S49" t="s">
-        <v>31</v>
-      </c>
-      <c r="T49" t="s">
-        <v>32</v>
-      </c>
-      <c r="U49" t="s">
-        <v>33</v>
-      </c>
-      <c r="V49" t="s">
-        <v>34</v>
-      </c>
-      <c r="W49" t="s">
-        <v>35</v>
-      </c>
-      <c r="X49" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y49" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z49" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB49" t="s">
-        <v>40</v>
+      <c r="B49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA49" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="3">
         <v>0.15754189944134001</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="3">
         <v>0.13935483870967699</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="3">
         <v>0.14323607427055701</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="3">
         <v>0.17631224764468301</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="3">
         <v>0.15921787709497201</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="3">
         <v>0.154185022026431</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="3">
         <v>0.15210355987054999</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="3">
         <v>0.19852941176470501</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="3">
         <v>0.154897494305239</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="3">
         <v>0.20198675496688701</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="3">
         <v>0.15846994535519099</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="3">
         <v>0.15116279069767399</v>
       </c>
-      <c r="N50">
+      <c r="N50" s="3">
         <v>0.16666666666666599</v>
       </c>
-      <c r="O50">
+      <c r="O50" s="3">
         <v>0.214285714285714</v>
       </c>
-      <c r="P50">
+      <c r="P50" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -16902,85 +16918,85 @@
       <c r="A51" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="3">
         <v>0.35799522673030998</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="3">
         <v>0.33920704845814897</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="3">
         <v>0.27751196172248799</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="3">
         <v>0.34634146341463401</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="3">
         <v>0.35353535353535298</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="3">
         <v>0.33163265306122403</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="3">
         <v>0.35</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="3">
         <v>0.37078651685393199</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="3">
         <v>0.33812949640287698</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="3">
         <v>0.43877551020408101</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="3">
         <v>0.16393442622950799</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="3">
         <v>0.31818181818181801</v>
       </c>
-      <c r="N51">
+      <c r="N51" s="3">
         <v>0.37837837837837801</v>
       </c>
-      <c r="O51">
+      <c r="O51" s="3">
         <v>0.39393939393939298</v>
       </c>
-      <c r="P51">
+      <c r="P51" s="3">
         <v>0.233333333333333</v>
       </c>
-      <c r="Q51">
+      <c r="Q51" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="R51">
+      <c r="R51" s="3">
         <v>0.44444444444444398</v>
       </c>
-      <c r="S51">
+      <c r="S51" s="3">
         <v>0.53333333333333299</v>
       </c>
-      <c r="T51">
+      <c r="T51" s="3">
         <v>0.38461538461538403</v>
       </c>
-      <c r="U51">
+      <c r="U51" s="3">
         <v>0.45454545454545398</v>
       </c>
-      <c r="V51">
+      <c r="V51" s="3">
         <v>0.53846153846153799</v>
       </c>
-      <c r="W51">
+      <c r="W51" s="3">
         <v>0</v>
       </c>
-      <c r="X51">
+      <c r="X51" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="Y51">
+      <c r="Y51" s="3">
         <v>1</v>
       </c>
-      <c r="Z51">
+      <c r="Z51" s="3">
         <v>0.6</v>
       </c>
-      <c r="AA51">
+      <c r="AA51" s="3">
         <v>0.5</v>
       </c>
-      <c r="AB51">
+      <c r="AB51" s="3">
         <v>1</v>
       </c>
     </row>
@@ -16988,40 +17004,40 @@
       <c r="A52" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="3">
         <v>0.21608040201004999</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="3">
         <v>0.23499577345731101</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="3">
         <v>0.21153846153846101</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="3">
         <v>0.25236294896030198</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="3">
         <v>0.224288840262582</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="3">
         <v>0.24495289367429299</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="3">
         <v>0.22678571428571401</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="3">
         <v>0.234848484848484</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="3">
         <v>0.203252032520325</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="3">
         <v>0.22115384615384601</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="3">
         <v>0.45161290322580599</v>
       </c>
-      <c r="M52">
+      <c r="M52" s="3">
         <v>0.4</v>
       </c>
     </row>
@@ -17029,46 +17045,46 @@
       <c r="A53" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="3">
         <v>0.28612716763005702</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="3">
         <v>0.31395348837209303</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="3">
         <v>0.28486646884272998</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="3">
         <v>0.298192771084337</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="3">
         <v>0.28846153846153799</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="3">
         <v>0.273037542662116</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="3">
         <v>0.26041666666666602</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="3">
         <v>0.31386861313868603</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="3">
         <v>0.30125523012552302</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="3">
         <v>0.33678756476683902</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="3">
         <v>0.33663366336633599</v>
       </c>
-      <c r="M53">
+      <c r="M53" s="3">
         <v>0.38983050847457601</v>
       </c>
-      <c r="N53">
+      <c r="N53" s="3">
         <v>0.27272727272727199</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="3">
         <v>0.625</v>
       </c>
     </row>
@@ -17076,57 +17092,57 @@
       <c r="A54" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="3">
         <v>0.23804971319311599</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="3">
         <v>0.19179389312977099</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="3">
         <v>0.20439350525310401</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="3">
         <v>0.23422562141491299</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="3">
         <v>0.21878121878121801</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <v>0.21644120707596201</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="3">
         <v>0.219326818675352</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="3">
         <v>0.2073732718894</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="3">
         <v>0.18495684340320501</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="3">
         <v>0.20224719101123501</v>
       </c>
-      <c r="L54">
+      <c r="L54" s="3">
         <v>0.23976608187134499</v>
       </c>
-      <c r="M54">
+      <c r="M54" s="3">
         <v>0.214285714285714</v>
       </c>
-      <c r="N54">
+      <c r="N54" s="3">
         <v>0.244680851063829</v>
       </c>
-      <c r="O54">
+      <c r="O54" s="3">
         <v>0.37037037037037002</v>
       </c>
-      <c r="P54">
+      <c r="P54" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="Q54">
+      <c r="Q54" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
+      <c r="A55" s="4"/>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
@@ -17134,141 +17150,141 @@
       </c>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
+      <c r="A57" s="4"/>
     </row>
     <row r="58" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B58" t="s">
-        <v>41</v>
-      </c>
-      <c r="C58" t="s">
-        <v>42</v>
-      </c>
-      <c r="D58" t="s">
-        <v>43</v>
-      </c>
-      <c r="E58" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" t="s">
-        <v>45</v>
-      </c>
-      <c r="G58" t="s">
-        <v>46</v>
-      </c>
-      <c r="H58" t="s">
-        <v>47</v>
-      </c>
-      <c r="I58" t="s">
-        <v>48</v>
-      </c>
-      <c r="J58" t="s">
-        <v>49</v>
-      </c>
-      <c r="K58" t="s">
-        <v>50</v>
-      </c>
-      <c r="L58" t="s">
-        <v>51</v>
-      </c>
-      <c r="M58" t="s">
-        <v>52</v>
-      </c>
-      <c r="N58" t="s">
-        <v>53</v>
-      </c>
-      <c r="O58" t="s">
-        <v>54</v>
-      </c>
-      <c r="P58" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>56</v>
-      </c>
-      <c r="R58" t="s">
-        <v>57</v>
-      </c>
-      <c r="S58" t="s">
-        <v>58</v>
-      </c>
-      <c r="T58" t="s">
-        <v>59</v>
-      </c>
-      <c r="U58" t="s">
-        <v>60</v>
-      </c>
-      <c r="V58" t="s">
-        <v>61</v>
-      </c>
-      <c r="W58" t="s">
-        <v>62</v>
-      </c>
-      <c r="X58" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y58" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z58" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA58" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB58" t="s">
-        <v>67</v>
+      <c r="B58" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="3">
         <v>0.18973214285714199</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="3">
         <v>0.157142857142857</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="3">
         <v>0.21466666666666601</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="3">
         <v>0.27321668909824998</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="3">
         <v>0.18915159944367099</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <v>0.145985401459854</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="3">
         <v>0.163430420711974</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="3">
         <v>0.18795620437956201</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="3">
         <v>0.16018306636155599</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="3">
         <v>0.19666666666666599</v>
       </c>
-      <c r="L59">
+      <c r="L59" s="3">
         <v>0.143646408839779</v>
       </c>
-      <c r="M59">
+      <c r="M59" s="3">
         <v>0.15730337078651599</v>
       </c>
-      <c r="N59">
+      <c r="N59" s="3">
         <v>0.214285714285714</v>
       </c>
-      <c r="O59">
+      <c r="O59" s="3">
         <v>0.35714285714285698</v>
       </c>
-      <c r="P59">
+      <c r="P59" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -17276,85 +17292,85 @@
       <c r="A60" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="3">
         <v>0.34198113207547098</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="3">
         <v>0.35714285714285698</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="3">
         <v>0.38536585365853598</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="3">
         <v>0.33495145631067902</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="3">
         <v>0.29207920792079201</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <v>0.35714285714285698</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="3">
         <v>0.44318181818181801</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="3">
         <v>0.35057471264367801</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="3">
         <v>0.40845070422535201</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="3">
         <v>0.26373626373626302</v>
       </c>
-      <c r="L60">
+      <c r="L60" s="3">
         <v>0.25396825396825301</v>
       </c>
-      <c r="M60">
+      <c r="M60" s="3">
         <v>0.39024390243902402</v>
       </c>
-      <c r="N60">
+      <c r="N60" s="3">
         <v>0.25</v>
       </c>
-      <c r="O60">
+      <c r="O60" s="3">
         <v>0.17647058823529399</v>
       </c>
-      <c r="P60">
+      <c r="P60" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="3">
         <v>0.5</v>
       </c>
-      <c r="R60">
+      <c r="R60" s="3">
         <v>0.36842105263157798</v>
       </c>
-      <c r="S60">
+      <c r="S60" s="3">
         <v>0.5</v>
       </c>
-      <c r="T60">
+      <c r="T60" s="3">
         <v>0.53333333333333299</v>
       </c>
-      <c r="U60">
+      <c r="U60" s="3">
         <v>0.25</v>
       </c>
-      <c r="V60">
+      <c r="V60" s="3">
         <v>0.30769230769230699</v>
       </c>
-      <c r="W60">
+      <c r="W60" s="3">
         <v>0.5</v>
       </c>
-      <c r="X60">
+      <c r="X60" s="3">
         <v>0.44444444444444398</v>
       </c>
-      <c r="Y60">
+      <c r="Y60" s="3">
         <v>0.4</v>
       </c>
-      <c r="Z60">
+      <c r="Z60" s="3">
         <v>0.8</v>
       </c>
-      <c r="AA60">
+      <c r="AA60" s="3">
         <v>0.5</v>
       </c>
-      <c r="AB60">
+      <c r="AB60" s="3">
         <v>1</v>
       </c>
     </row>
@@ -17362,40 +17378,40 @@
       <c r="A61" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="3">
         <v>0.244949494949494</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="3">
         <v>0.244006849315068</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="3">
         <v>0.21447253705318201</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="3">
         <v>0.23424270931326399</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="3">
         <v>0.24505494505494499</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="3">
         <v>0.25871313672922203</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="3">
         <v>0.25</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="3">
         <v>0.209876543209876</v>
       </c>
-      <c r="J61">
+      <c r="J61" s="3">
         <v>0.21052631578947301</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="3">
         <v>0.28155339805825202</v>
       </c>
-      <c r="L61">
+      <c r="L61" s="3">
         <v>0.29032258064516098</v>
       </c>
-      <c r="M61">
+      <c r="M61" s="3">
         <v>0.83333333333333304</v>
       </c>
     </row>
@@ -17403,46 +17419,46 @@
       <c r="A62" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="3">
         <v>0.27034883720930197</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="3">
         <v>0.29512893982807997</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="3">
         <v>0.30994152046783602</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="3">
         <v>0.32530120481927699</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="3">
         <v>0.32371794871794801</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="3">
         <v>0.25170068027210801</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="3">
         <v>0.28873239436619702</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="3">
         <v>0.30258302583025798</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="3">
         <v>0.30672268907563</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="3">
         <v>0.28272251308900498</v>
       </c>
-      <c r="L62">
+      <c r="L62" s="3">
         <v>0.237623762376237</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="3">
         <v>0.25423728813559299</v>
       </c>
-      <c r="N62">
+      <c r="N62" s="3">
         <v>0.30434782608695599</v>
       </c>
-      <c r="O62">
+      <c r="O62" s="3">
         <v>0.375</v>
       </c>
     </row>
@@ -17450,65 +17466,65 @@
       <c r="A63" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="3">
         <v>0.242013552758954</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="3">
         <v>0.222862632084534</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="3">
         <v>0.21809523809523801</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="3">
         <v>0.21407907425265099</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="3">
         <v>0.19364448857993999</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="3">
         <v>0.22302904564315301</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="3">
         <v>0.21513513513513499</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="3">
         <v>0.241657077100115</v>
       </c>
-      <c r="J63">
+      <c r="J63" s="3">
         <v>0.22276621787025699</v>
       </c>
-      <c r="K63">
+      <c r="K63" s="3">
         <v>0.2328190743338</v>
       </c>
-      <c r="L63">
+      <c r="L63" s="3">
         <v>0.23346303501945501</v>
       </c>
-      <c r="M63">
+      <c r="M63" s="3">
         <v>0.21505376344086</v>
       </c>
-      <c r="N63">
+      <c r="N63" s="3">
         <v>0.28571428571428498</v>
       </c>
-      <c r="O63">
+      <c r="O63" s="3">
         <v>0.44444444444444398</v>
       </c>
-      <c r="P63">
+      <c r="P63" s="3">
         <v>0.28571428571428498</v>
       </c>
-      <c r="Q63">
+      <c r="Q63" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A64" s="3"/>
+      <c r="A64" s="4"/>
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A66" s="3"/>
+      <c r="A66" s="4"/>
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
@@ -17516,198 +17532,198 @@
       </c>
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
+      <c r="A68" s="4"/>
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B69" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" t="s">
-        <v>77</v>
-      </c>
-      <c r="D69" t="s">
-        <v>78</v>
-      </c>
-      <c r="E69" t="s">
-        <v>79</v>
-      </c>
-      <c r="F69" t="s">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s">
-        <v>82</v>
-      </c>
-      <c r="I69" t="s">
-        <v>83</v>
-      </c>
-      <c r="J69" t="s">
-        <v>84</v>
-      </c>
-      <c r="K69" t="s">
-        <v>85</v>
-      </c>
-      <c r="L69" t="s">
-        <v>86</v>
-      </c>
-      <c r="M69" t="s">
-        <v>87</v>
-      </c>
-      <c r="N69" t="s">
-        <v>88</v>
-      </c>
-      <c r="O69" t="s">
-        <v>89</v>
-      </c>
-      <c r="P69" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>91</v>
-      </c>
-      <c r="R69" t="s">
-        <v>92</v>
-      </c>
-      <c r="S69" t="s">
-        <v>93</v>
-      </c>
-      <c r="T69" t="s">
-        <v>94</v>
-      </c>
-      <c r="U69" t="s">
-        <v>95</v>
-      </c>
-      <c r="V69" t="s">
-        <v>96</v>
-      </c>
-      <c r="W69" t="s">
-        <v>97</v>
-      </c>
-      <c r="X69" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA69" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB69" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC69" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD69" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE69" t="s">
-        <v>105</v>
-      </c>
-      <c r="AF69" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG69" t="s">
-        <v>107</v>
+      <c r="B69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P69" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q69" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R69" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T69" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U69" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V69" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W69" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z69" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA69" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB69" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD69" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE69" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG69" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="3">
         <v>0.35356200527704401</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="3">
         <v>0.173267326732673</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="3">
         <v>0.171018276762402</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="3">
         <v>0.17069701280227501</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="3">
         <v>0.124031007751937</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="3">
         <v>0.14285714285714199</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="3">
         <v>0.120567375886524</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="3">
         <v>0.20648967551622399</v>
       </c>
-      <c r="J70">
+      <c r="J70" s="3">
         <v>0.20522388059701399</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="3">
         <v>0.133663366336633</v>
       </c>
-      <c r="L70">
+      <c r="L70" s="3">
         <v>0.124260355029585</v>
       </c>
-      <c r="M70">
+      <c r="M70" s="3">
         <v>0.14765100671140899</v>
       </c>
-      <c r="N70">
+      <c r="N70" s="3">
         <v>0.19858156028368701</v>
       </c>
-      <c r="O70">
+      <c r="O70" s="3">
         <v>0.10344827586206801</v>
       </c>
-      <c r="P70">
+      <c r="P70" s="3">
         <v>0.247422680412371</v>
       </c>
-      <c r="Q70">
+      <c r="Q70" s="3">
         <v>0.146341463414634</v>
       </c>
-      <c r="R70">
+      <c r="R70" s="3">
         <v>0.108108108108108</v>
       </c>
-      <c r="S70">
+      <c r="S70" s="3">
         <v>0.305084745762711</v>
       </c>
-      <c r="T70">
+      <c r="T70" s="3">
         <v>0.35555555555555501</v>
       </c>
-      <c r="U70">
+      <c r="U70" s="3">
         <v>0.25</v>
       </c>
-      <c r="V70">
+      <c r="V70" s="3">
         <v>0.27272727272727199</v>
       </c>
-      <c r="W70">
+      <c r="W70" s="3">
         <v>0.2</v>
       </c>
-      <c r="X70">
+      <c r="X70" s="3">
         <v>0.29166666666666602</v>
       </c>
-      <c r="Y70">
+      <c r="Y70" s="3">
         <v>0.31034482758620602</v>
       </c>
-      <c r="Z70">
+      <c r="Z70" s="3">
         <v>0.23076923076923</v>
       </c>
-      <c r="AA70">
+      <c r="AA70" s="3">
         <v>0.25</v>
       </c>
-      <c r="AB70">
+      <c r="AB70" s="3">
         <v>0.25</v>
       </c>
-      <c r="AC70">
+      <c r="AC70" s="3">
         <v>0.35714285714285698</v>
       </c>
-      <c r="AD70">
+      <c r="AD70" s="3">
         <v>0.33333333333333298</v>
       </c>
     </row>
@@ -17715,31 +17731,31 @@
       <c r="A71" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="3">
         <v>0.51521739130434696</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="3">
         <v>0.27976190476190399</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="3">
         <v>0.27213822894168399</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="3">
         <v>0.30199430199430199</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="3">
         <v>0.29729729729729698</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="3">
         <v>0.263636363636363</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="3">
         <v>0.42592592592592499</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="3">
         <v>0.47368421052631499</v>
       </c>
-      <c r="J71">
+      <c r="J71" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -17747,100 +17763,100 @@
       <c r="A72" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="3">
         <v>0.46482213438735098</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="3">
         <v>0.20514761544284599</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="3">
         <v>0.21937086092715199</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="3">
         <v>0.20189274447949501</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="3">
         <v>0.25072463768115899</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="3">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="3">
         <v>0.25882352941176401</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="3">
         <v>0.262357414448669</v>
       </c>
-      <c r="J72">
+      <c r="J72" s="3">
         <v>0.25268817204300997</v>
       </c>
-      <c r="K72">
+      <c r="K72" s="3">
         <v>0.211920529801324</v>
       </c>
-      <c r="L72">
+      <c r="L72" s="3">
         <v>0.28282828282828198</v>
       </c>
-      <c r="M72">
+      <c r="M72" s="3">
         <v>0.28282828282828198</v>
       </c>
-      <c r="N72">
+      <c r="N72" s="3">
         <v>0.17241379310344801</v>
       </c>
-      <c r="O72">
+      <c r="O72" s="3">
         <v>0.35593220338983</v>
       </c>
-      <c r="P72">
+      <c r="P72" s="3">
         <v>0.19148936170212699</v>
       </c>
-      <c r="Q72">
+      <c r="Q72" s="3">
         <v>0.35483870967741898</v>
       </c>
-      <c r="R72">
+      <c r="R72" s="3">
         <v>0.42857142857142799</v>
       </c>
-      <c r="S72">
+      <c r="S72" s="3">
         <v>0.32</v>
       </c>
-      <c r="T72">
+      <c r="T72" s="3">
         <v>0.42857142857142799</v>
       </c>
-      <c r="U72">
+      <c r="U72" s="3">
         <v>0.238095238095238</v>
       </c>
-      <c r="V72">
+      <c r="V72" s="3">
         <v>0.30434782608695599</v>
       </c>
-      <c r="W72">
+      <c r="W72" s="3">
         <v>0.42105263157894701</v>
       </c>
-      <c r="X72">
+      <c r="X72" s="3">
         <v>0.6</v>
       </c>
-      <c r="Y72">
+      <c r="Y72" s="3">
         <v>0.4</v>
       </c>
-      <c r="Z72">
+      <c r="Z72" s="3">
         <v>0.4</v>
       </c>
-      <c r="AA72">
+      <c r="AA72" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="AB72">
+      <c r="AB72" s="3">
         <v>0.3</v>
       </c>
-      <c r="AC72">
+      <c r="AC72" s="3">
         <v>0.55555555555555503</v>
       </c>
-      <c r="AD72">
+      <c r="AD72" s="3">
         <v>0.75</v>
       </c>
-      <c r="AE72">
+      <c r="AE72" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="AF72">
+      <c r="AF72" s="3">
         <v>0.25</v>
       </c>
-      <c r="AG72">
+      <c r="AG72" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -17848,43 +17864,43 @@
       <c r="A73" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="3">
         <v>0.52869565217391301</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="3">
         <v>0.30990415335463201</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="3">
         <v>0.31672597864768598</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="3">
         <v>0.28384279475982499</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="3">
         <v>0.302702702702702</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="3">
         <v>0.36244541484716097</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="3">
         <v>0.25242718446601897</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="3">
         <v>0.31666666666666599</v>
       </c>
-      <c r="J73">
+      <c r="J73" s="3">
         <v>0.34693877551020402</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="3">
         <v>0.3125</v>
       </c>
-      <c r="L73">
+      <c r="L73" s="3">
         <v>0.38461538461538403</v>
       </c>
-      <c r="M73">
+      <c r="M73" s="3">
         <v>0.28571428571428498</v>
       </c>
-      <c r="N73">
+      <c r="N73" s="3">
         <v>0.23076923076923</v>
       </c>
     </row>
@@ -17892,99 +17908,99 @@
       <c r="A74" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="3">
         <v>0.441046551138294</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="3">
         <v>0.297094017094017</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="3">
         <v>0.23365928975810599</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="3">
         <v>0.221884498480243</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="3">
         <v>0.19570405727923601</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="3">
         <v>0.148148148148148</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="3">
         <v>0.27692307692307599</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="3">
         <v>0.16831683168316799</v>
       </c>
-      <c r="J74">
+      <c r="J74" s="3">
         <v>0.232876712328767</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="3">
         <v>0.29824561403508698</v>
       </c>
-      <c r="L74">
+      <c r="L74" s="3">
         <v>0.407407407407407</v>
       </c>
-      <c r="M74">
+      <c r="M74" s="3">
         <v>0.22222222222222199</v>
       </c>
-      <c r="N74">
+      <c r="N74" s="3">
         <v>0.203703703703703</v>
       </c>
-      <c r="O74">
+      <c r="O74" s="3">
         <v>0.232558139534883</v>
       </c>
-      <c r="P74">
+      <c r="P74" s="3">
         <v>0.27500000000000002</v>
       </c>
-      <c r="Q74">
+      <c r="Q74" s="3">
         <v>0.17499999999999999</v>
       </c>
-      <c r="R74">
+      <c r="R74" s="3">
         <v>0.27027027027027001</v>
       </c>
-      <c r="S74">
+      <c r="S74" s="3">
         <v>0.441176470588235</v>
       </c>
-      <c r="T74">
+      <c r="T74" s="3">
         <v>0.314285714285714</v>
       </c>
-      <c r="U74">
+      <c r="U74" s="3">
         <v>0.434782608695652</v>
       </c>
-      <c r="V74">
+      <c r="V74" s="3">
         <v>0.34615384615384598</v>
       </c>
-      <c r="W74">
+      <c r="W74" s="3">
         <v>0.28000000000000003</v>
       </c>
-      <c r="X74">
+      <c r="X74" s="3">
         <v>0.434782608695652</v>
       </c>
-      <c r="Y74">
+      <c r="Y74" s="3">
         <v>0.375</v>
       </c>
-      <c r="Z74">
+      <c r="Z74" s="3">
         <v>0.53333333333333299</v>
       </c>
-      <c r="AA74">
+      <c r="AA74" s="3">
         <v>0.77777777777777701</v>
       </c>
-      <c r="AB74">
+      <c r="AB74" s="3">
         <v>0.55555555555555503</v>
       </c>
-      <c r="AC74">
+      <c r="AC74" s="3">
         <v>0.53846153846153799</v>
       </c>
-      <c r="AD74">
+      <c r="AD74" s="3">
         <v>0.63636363636363602</v>
       </c>
-      <c r="AE74">
+      <c r="AE74" s="3">
         <v>0.4</v>
       </c>
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
+      <c r="A75" s="4"/>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
@@ -17992,198 +18008,198 @@
       </c>
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
+      <c r="A77" s="4"/>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B78" t="s">
-        <v>76</v>
-      </c>
-      <c r="C78" t="s">
-        <v>77</v>
-      </c>
-      <c r="D78" t="s">
-        <v>78</v>
-      </c>
-      <c r="E78" t="s">
-        <v>79</v>
-      </c>
-      <c r="F78" t="s">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s">
-        <v>82</v>
-      </c>
-      <c r="I78" t="s">
-        <v>83</v>
-      </c>
-      <c r="J78" t="s">
-        <v>84</v>
-      </c>
-      <c r="K78" t="s">
-        <v>85</v>
-      </c>
-      <c r="L78" t="s">
-        <v>86</v>
-      </c>
-      <c r="M78" t="s">
-        <v>87</v>
-      </c>
-      <c r="N78" t="s">
-        <v>88</v>
-      </c>
-      <c r="O78" t="s">
-        <v>89</v>
-      </c>
-      <c r="P78" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>91</v>
-      </c>
-      <c r="R78" t="s">
-        <v>92</v>
-      </c>
-      <c r="S78" t="s">
-        <v>93</v>
-      </c>
-      <c r="T78" t="s">
-        <v>94</v>
-      </c>
-      <c r="U78" t="s">
-        <v>95</v>
-      </c>
-      <c r="V78" t="s">
-        <v>96</v>
-      </c>
-      <c r="W78" t="s">
-        <v>97</v>
-      </c>
-      <c r="X78" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y78" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA78" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB78" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC78" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD78" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE78" t="s">
-        <v>105</v>
-      </c>
-      <c r="AF78" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG78" t="s">
-        <v>107</v>
+      <c r="B78" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q78" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R78" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T78" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U78" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V78" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W78" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z78" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA78" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB78" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC78" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD78" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE78" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG78" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="3">
         <v>0.16427640156453699</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="3">
         <v>0.19753086419752999</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="3">
         <v>0.19790301441677499</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="3">
         <v>0.16499282639885199</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="3">
         <v>0.18266253869969001</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="3">
         <v>0.15196998123827299</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="3">
         <v>0.17857142857142799</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="3">
         <v>0.15697674418604601</v>
       </c>
-      <c r="J79">
+      <c r="J79" s="3">
         <v>0.189393939393939</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="3">
         <v>0.133663366336633</v>
       </c>
-      <c r="L79">
+      <c r="L79" s="3">
         <v>0.14117647058823499</v>
       </c>
-      <c r="M79">
+      <c r="M79" s="3">
         <v>0.16551724137931001</v>
       </c>
-      <c r="N79">
+      <c r="N79" s="3">
         <v>0.18115942028985499</v>
       </c>
-      <c r="O79">
+      <c r="O79" s="3">
         <v>0.17391304347826</v>
       </c>
-      <c r="P79">
+      <c r="P79" s="3">
         <v>0.221052631578947</v>
       </c>
-      <c r="Q79">
+      <c r="Q79" s="3">
         <v>0.13095238095237999</v>
       </c>
-      <c r="R79">
+      <c r="R79" s="3">
         <v>8.2191780821917804E-2</v>
       </c>
-      <c r="S79">
+      <c r="S79" s="3">
         <v>0.18965517241379301</v>
       </c>
-      <c r="T79">
+      <c r="T79" s="3">
         <v>0.217391304347826</v>
       </c>
-      <c r="U79">
+      <c r="U79" s="3">
         <v>0.135135135135135</v>
       </c>
-      <c r="V79">
+      <c r="V79" s="3">
         <v>0.24242424242424199</v>
       </c>
-      <c r="W79">
+      <c r="W79" s="3">
         <v>0.12</v>
       </c>
-      <c r="X79">
+      <c r="X79" s="3">
         <v>0.24</v>
       </c>
-      <c r="Y79">
+      <c r="Y79" s="3">
         <v>0.266666666666666</v>
       </c>
-      <c r="Z79">
+      <c r="Z79" s="3">
         <v>0.12</v>
       </c>
-      <c r="AA79">
+      <c r="AA79" s="3">
         <v>0.3</v>
       </c>
-      <c r="AB79">
+      <c r="AB79" s="3">
         <v>0</v>
       </c>
-      <c r="AC79">
+      <c r="AC79" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="AD79">
+      <c r="AD79" s="3">
         <v>0.33333333333333298</v>
       </c>
     </row>
@@ -18191,31 +18207,31 @@
       <c r="A80" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="3">
         <v>0.34557235421166299</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="3">
         <v>0.39376218323586698</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="3">
         <v>0.39689578713968898</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="3">
         <v>0.4</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="3">
         <v>0.287292817679558</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="3">
         <v>0.394230769230769</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="3">
         <v>0.23214285714285701</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="3">
         <v>0.38888888888888801</v>
       </c>
-      <c r="J80">
+      <c r="J80" s="3">
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -18223,100 +18239,100 @@
       <c r="A81" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="3">
         <v>0.303006329113924</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="3">
         <v>0.25731432858214498</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="3">
         <v>0.23554065381391401</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="3">
         <v>0.24344176285414401</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="3">
         <v>0.21313868613138601</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="3">
         <v>0.249496981891348</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="3">
         <v>0.212389380530973</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="3">
         <v>0.22097378277153501</v>
       </c>
-      <c r="J81">
+      <c r="J81" s="3">
         <v>0.221052631578947</v>
       </c>
-      <c r="K81">
+      <c r="K81" s="3">
         <v>0.22222222222222199</v>
       </c>
-      <c r="L81">
+      <c r="L81" s="3">
         <v>0.26732673267326701</v>
       </c>
-      <c r="M81">
+      <c r="M81" s="3">
         <v>0.2</v>
       </c>
-      <c r="N81">
+      <c r="N81" s="3">
         <v>0.21176470588235199</v>
       </c>
-      <c r="O81">
+      <c r="O81" s="3">
         <v>0.24561403508771901</v>
       </c>
-      <c r="P81">
+      <c r="P81" s="3">
         <v>0.24489795918367299</v>
       </c>
-      <c r="Q81">
+      <c r="Q81" s="3">
         <v>0.41935483870967699</v>
       </c>
-      <c r="R81">
+      <c r="R81" s="3">
         <v>0.35714285714285698</v>
       </c>
-      <c r="S81">
+      <c r="S81" s="3">
         <v>0.48</v>
       </c>
-      <c r="T81">
+      <c r="T81" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="U81">
+      <c r="U81" s="3">
         <v>0.36363636363636298</v>
       </c>
-      <c r="V81">
+      <c r="V81" s="3">
         <v>0.40909090909090901</v>
       </c>
-      <c r="W81">
+      <c r="W81" s="3">
         <v>0.31578947368421001</v>
       </c>
-      <c r="X81">
+      <c r="X81" s="3">
         <v>0.53333333333333299</v>
       </c>
-      <c r="Y81">
+      <c r="Y81" s="3">
         <v>0.5</v>
       </c>
-      <c r="Z81">
+      <c r="Z81" s="3">
         <v>0.4</v>
       </c>
-      <c r="AA81">
+      <c r="AA81" s="3">
         <v>0.5</v>
       </c>
-      <c r="AB81">
+      <c r="AB81" s="3">
         <v>0.5</v>
       </c>
-      <c r="AC81">
+      <c r="AC81" s="3">
         <v>0.25</v>
       </c>
-      <c r="AD81">
+      <c r="AD81" s="3">
         <v>0.6</v>
       </c>
-      <c r="AE81">
+      <c r="AE81" s="3">
         <v>0.33333333333333298</v>
       </c>
-      <c r="AF81">
+      <c r="AF81" s="3">
         <v>0.75</v>
       </c>
-      <c r="AG81">
+      <c r="AG81" s="3">
         <v>0.33333333333333298</v>
       </c>
     </row>
@@ -18324,43 +18340,43 @@
       <c r="A82" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="3">
         <v>0.29432013769363102</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="3">
         <v>0.29606299212598403</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="3">
         <v>0.31059245960502602</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="3">
         <v>0.30652173913043401</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="3">
         <v>0.32054794520547902</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="3">
         <v>0.24107142857142799</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="3">
         <v>0.28155339805825202</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="3">
         <v>0.28333333333333299</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="3">
         <v>0.28888888888888797</v>
       </c>
-      <c r="K82">
+      <c r="K82" s="3">
         <v>0.35294117647058798</v>
       </c>
-      <c r="L82">
+      <c r="L82" s="3">
         <v>0.48</v>
       </c>
-      <c r="M82">
+      <c r="M82" s="3">
         <v>0.266666666666666</v>
       </c>
-      <c r="N82">
+      <c r="N82" s="3">
         <v>0.53846153846153799</v>
       </c>
     </row>
@@ -18368,99 +18384,99 @@
       <c r="A83" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="3">
         <v>0.235970250169033</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="3">
         <v>0.22816032887975299</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="3">
         <v>0.213884635017866</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="3">
         <v>0.22233606557377</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="3">
         <v>0.21634615384615299</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="3">
         <v>0.22065727699530499</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="3">
         <v>0.186046511627906</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="3">
         <v>0.25</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="3">
         <v>0.30555555555555503</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="3">
         <v>0.25862068965517199</v>
       </c>
-      <c r="L83">
+      <c r="L83" s="3">
         <v>0.26315789473684198</v>
       </c>
-      <c r="M83">
+      <c r="M83" s="3">
         <v>0.2</v>
       </c>
-      <c r="N83">
+      <c r="N83" s="3">
         <v>0.31578947368421001</v>
       </c>
-      <c r="O83">
+      <c r="O83" s="3">
         <v>0.38095238095237999</v>
       </c>
-      <c r="P83">
+      <c r="P83" s="3">
         <v>0.35</v>
       </c>
-      <c r="Q83">
+      <c r="Q83" s="3">
         <v>0.37837837837837801</v>
       </c>
-      <c r="R83">
+      <c r="R83" s="3">
         <v>0.45714285714285702</v>
       </c>
-      <c r="S83">
+      <c r="S83" s="3">
         <v>0.38235294117647001</v>
       </c>
-      <c r="T83">
+      <c r="T83" s="3">
         <v>0.29411764705882298</v>
       </c>
-      <c r="U83">
+      <c r="U83" s="3">
         <v>0.41666666666666602</v>
       </c>
-      <c r="V83">
+      <c r="V83" s="3">
         <v>0.23076923076923</v>
       </c>
-      <c r="W83">
+      <c r="W83" s="3">
         <v>0.375</v>
       </c>
-      <c r="X83">
+      <c r="X83" s="3">
         <v>0.45454545454545398</v>
       </c>
-      <c r="Y83">
+      <c r="Y83" s="3">
         <v>0.30434782608695599</v>
       </c>
-      <c r="Z83">
+      <c r="Z83" s="3">
         <v>0.266666666666666</v>
       </c>
-      <c r="AA83">
+      <c r="AA83" s="3">
         <v>0.44444444444444398</v>
       </c>
-      <c r="AB83">
+      <c r="AB83" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="AC83">
+      <c r="AC83" s="3">
         <v>0.30769230769230699</v>
       </c>
-      <c r="AD83">
+      <c r="AD83" s="3">
         <v>0.72727272727272696</v>
       </c>
-      <c r="AE83">
+      <c r="AE83" s="3">
         <v>0.8</v>
       </c>
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A84" s="3"/>
+      <c r="A84" s="4"/>
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
